--- a/09_products.xlsx
+++ b/09_products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
   <si>
     <t>product_id</t>
   </si>
@@ -22,21 +22,111 @@
     <t>product_type</t>
   </si>
   <si>
-    <t>base_price</t>
+    <t>price</t>
   </si>
   <si>
     <t>subscription_period</t>
   </si>
   <si>
+    <t>business_line</t>
+  </si>
+  <si>
+    <t>course_id</t>
+  </si>
+  <si>
     <t>conditions</t>
   </si>
   <si>
-    <t>business_line</t>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>Excel для бизнеса</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>B2B/B2C</t>
+  </si>
+  <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t>Полный доступ к курсу</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>Управление проектами</t>
+  </si>
+  <si>
+    <t>B2B</t>
+  </si>
+  <si>
+    <t>C002</t>
+  </si>
+  <si>
+    <t>Доступ 1 год</t>
   </si>
   <si>
     <t>P003</t>
   </si>
   <si>
+    <t>Лидерство</t>
+  </si>
+  <si>
+    <t>C003</t>
+  </si>
+  <si>
+    <t>Полный доступ</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>Аналитика данных</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Переговоры</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>Финансы для нефинансистов</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>Python для начинающих</t>
+  </si>
+  <si>
+    <t>B2C</t>
+  </si>
+  <si>
+    <t>C008</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
     <t>Корпоративная подписка "Базовый"</t>
   </si>
   <si>
@@ -49,10 +139,7 @@
     <t>Доступ к 10 курсам из каталога</t>
   </si>
   <si>
-    <t>B2B</t>
-  </si>
-  <si>
-    <t>P005</t>
+    <t>P009</t>
   </si>
   <si>
     <t>Подписка "Pro"</t>
@@ -64,7 +151,7 @@
     <t>Полный доступ ко всем курсам + премиум-поддержка</t>
   </si>
   <si>
-    <t>P006</t>
+    <t>P010</t>
   </si>
   <si>
     <t>Доступ к библиотеке курсов</t>
@@ -76,10 +163,7 @@
     <t>100+ курсов, обновление ежеквартально</t>
   </si>
   <si>
-    <t>B2B/B2C</t>
-  </si>
-  <si>
-    <t>P007</t>
+    <t>P011</t>
   </si>
   <si>
     <t>Премиум-поддержка</t>
@@ -91,49 +175,22 @@
     <t>SLA 2 часа, персональный менеджер</t>
   </si>
   <si>
-    <t>P008</t>
+    <t>P012</t>
   </si>
   <si>
     <t>Индивидуальная разработка курса</t>
   </si>
   <si>
-    <t>NULL</t>
-  </si>
-  <si>
     <t>Под ключ, срок 1-3 месяца</t>
   </si>
   <si>
-    <t>P009</t>
-  </si>
-  <si>
-    <t>Аудит корпоративного обучения</t>
-  </si>
-  <si>
-    <t>Разовый аудит с отчетом</t>
-  </si>
-  <si>
-    <t>P010</t>
-  </si>
-  <si>
-    <t>Тестовый доступ</t>
-  </si>
-  <si>
-    <t>week</t>
-  </si>
-  <si>
-    <t>Для ознакомления</t>
-  </si>
-  <si>
-    <t>marketing</t>
-  </si>
-  <si>
-    <t>P011</t>
+    <t>P013</t>
   </si>
   <si>
     <t>Корпоративная подписка "Lite"</t>
   </si>
   <si>
-    <t>Доступ к 5 курсам из каталога</t>
+    <t>Доступ к 5 курсам</t>
   </si>
 </sst>
 </file>
@@ -402,7 +459,8 @@
     <col customWidth="1" min="2" max="2" width="34.25"/>
     <col customWidth="1" min="3" max="3" width="12.63"/>
     <col customWidth="1" min="5" max="5" width="18.38"/>
-    <col customWidth="1" min="6" max="6" width="51.0"/>
+    <col customWidth="1" min="6" max="6" width="13.13"/>
+    <col customWidth="1" min="8" max="8" width="51.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -427,120 +485,138 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1">
-        <v>35000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>150000.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1">
-        <v>250000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>200000.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1">
-        <v>50000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>150000.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1">
-        <v>75000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="2">
+        <v>250000.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1">
-        <v>150000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>180000.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
+      <c r="H6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -551,19 +627,22 @@
         <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1">
-        <v>95000.0</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="2">
+        <v>220000.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -574,42 +653,176 @@
         <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.0</v>
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>280000.0</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>37</v>
+      <c r="H8" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1">
-        <v>30000.0</v>
+      <c r="D9" s="2">
+        <v>250000.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2">
+        <v>350000.0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50000.0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2">
+        <v>75000.0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="1">
+        <v>150000.0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2">
+        <v>200000.0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
